--- a/output/pdf_financials_xlsx/WCP.xlsx
+++ b/output/pdf_financials_xlsx/WCP.xlsx
@@ -2074,19 +2074,19 @@
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>9.771000000000001</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>48.976</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>119.598</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>152.387</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>258.141</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0</v>
@@ -2110,10 +2110,10 @@
         <v>0</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.0008652</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.0009752000000000001</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>0</v>
@@ -2129,19 +2129,19 @@
         <v>-1.645</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-9.074</v>
+        <v>0.697</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>34.692</v>
+        <v>83.66800000000001</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>72.935</v>
+        <v>192.533</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>65.411</v>
+        <v>217.798</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>551.3</v>
+        <v>809.441</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-608.075</v>
@@ -2165,10 +2165,10 @@
         <v>0.0022246</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.0011707</v>
+        <v>0.0020359</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.0010753</v>
+        <v>0.0020505</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>0.0013256</v>
@@ -2184,19 +2184,19 @@
         <v>-42.33144621718991</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-40.44392939917989</v>
+        <v>3.106614369762881</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>28.65544413790825</v>
+        <v>69.10941139543721</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>26.94221470287282</v>
+        <v>71.12175805015718</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>16.37928444079409</v>
+        <v>54.537851319137</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>53.01450903160292</v>
+        <v>77.8380504354248</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>-126.2645663928503</v>
@@ -6100,19 +6100,19 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>9.771000000000001</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>48.976</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>119.598</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>152.387</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>258.141</v>
       </c>
       <c r="H100" s="3" t="n">
         <v>0</v>
@@ -6136,10 +6136,10 @@
         <v>0</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.0008652</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.0009752000000000001</v>
       </c>
       <c r="Q100" s="3" t="n">
         <v>0</v>
@@ -33208,7 +33208,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -43908,7 +43908,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -53290,7 +53290,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">

--- a/output/pdf_financials_xlsx/WCP.xlsx
+++ b/output/pdf_financials_xlsx/WCP.xlsx
@@ -941,28 +941,28 @@
         <v>296.358</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1070.863</v>
+        <v>1080.466</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>1222.137</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>1295.662</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.0001558</v>
+        <v>0.0003883</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.000313</v>
+        <v>0.0015158</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.0002739</v>
+        <v>0.002211</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.0002533</v>
+        <v>0.0022462</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.0002484</v>
+        <v>0.0041855</v>
       </c>
     </row>
     <row r="11">
@@ -996,7 +996,7 @@
         <v>239.619</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-160.623</v>
+        <v>-170.226</v>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0</v>
@@ -2423,10 +2423,10 @@
         <v>0</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.0003623</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>5.94e-05</v>
       </c>
     </row>
     <row r="35">
@@ -2491,16 +2491,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.0003623</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>5.94e-05</v>
       </c>
     </row>
     <row r="37">
@@ -3151,16 +3151,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.143569</v>
+        <v>0.138569</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.254</v>
+        <v>1.241</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>36.452</v>
+        <v>36.44</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>11.628</v>
@@ -3193,10 +3193,10 @@
         <v>0.0001113</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.0004621</v>
+        <v>9.979999999999996e-05</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.0003393999999999998</v>
+        <v>0.0002799999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -7453,16 +7453,16 @@
         <v>-28.534</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-10.631</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-6.9e-06</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-4.1e-06</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-7e-06</v>
       </c>
       <c r="P124" s="3" t="n">
         <v>0</v>
@@ -7508,16 +7508,16 @@
         <v>-28.534</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-10.631</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-6.9e-06</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-4.1e-06</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-7e-06</v>
       </c>
       <c r="P125" s="3" t="n">
         <v>0</v>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -25966,7 +25966,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -27496,7 +27496,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -34690,7 +34690,11 @@
           <t>Principal portion of lease payments</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -52382,7 +52386,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
@@ -52435,7 +52439,7 @@
         <v>1295.662</v>
       </c>
       <c r="P473" s="5" t="n">
-        <v>-0.0003883</v>
+        <v>0.0003883</v>
       </c>
       <c r="Q473" s="5" t="n">
         <v>0.0015158</v>

--- a/output/pdf_financials_xlsx/WCP.xlsx
+++ b/output/pdf_financials_xlsx/WCP.xlsx
@@ -3629,46 +3629,46 @@
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>609.244</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>1467.644</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>2175.756</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>3938.372</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>5132.458</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>5956.364</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>7323.147</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>7881.499</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
+        <v>8425.299999999999</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0</v>
+        <v>0.0112437</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0</v>
+        <v>0.0129058</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0</v>
+        <v>0.0141787</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>0</v>
+        <v>0.0151144</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>0</v>
+        <v>0.0247907</v>
       </c>
     </row>
     <row r="57">
@@ -4458,19 +4458,19 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>3.5e-06</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>6.599999999999999e-06</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>7.8e-06</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>1.54e-05</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>6.31e-05</v>
       </c>
     </row>
     <row r="71">
@@ -4513,19 +4513,19 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>3.5e-06</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>6.599999999999999e-06</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>7.8e-06</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>1.54e-05</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0.000195</v>
+        <v>0.0002581</v>
       </c>
     </row>
     <row r="72">
@@ -4733,19 +4733,19 @@
         <v>33.41</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.0001391</v>
+        <v>0.0001356</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.0002051</v>
+        <v>0.0001985</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>5.860000000000002e-05</v>
+        <v>5.080000000000007e-05</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>6.929999999999995e-05</v>
+        <v>5.389999999999998e-05</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>0.0001618999999999999</v>
+        <v>9.879999999999973e-05</v>
       </c>
     </row>
     <row r="76">
@@ -5030,19 +5030,19 @@
         </is>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.2823180189335188</v>
+        <v>0.2832539979675884</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.3652890270709151</v>
+        <v>0.366596035408044</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.2475990505751323</v>
+        <v>0.2490231878765747</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.178135820298227</v>
+        <v>0.1808153393767508</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0.2787351620584974</v>
+        <v>0.2844703786515424</v>
       </c>
     </row>
     <row r="81">
@@ -6680,19 +6680,19 @@
         <v>0</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>2.43e-05</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>3.629999999999999e-05</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>3.36e-05</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>3.73e-05</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>5.03e-05</v>
       </c>
     </row>
     <row r="111">
@@ -7395,10 +7395,10 @@
         <v>0</v>
       </c>
       <c r="K123" s="3" t="n">
-        <v>0</v>
+        <v>-28.534</v>
       </c>
       <c r="L123" s="3" t="n">
-        <v>0</v>
+        <v>-79.497</v>
       </c>
       <c r="M123" s="3" t="n">
         <v>0</v>
@@ -7505,10 +7505,10 @@
         <v>-83.633</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>-28.534</v>
+        <v>-57.068</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>-10.631</v>
+        <v>-90.128</v>
       </c>
       <c r="M125" s="3" t="n">
         <v>-6.9e-06</v>
@@ -9628,7 +9628,11 @@
           <t>Lease liabilities 11</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -11684,7 +11688,11 @@
           <t>Lease liabilities 12</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -31994,7 +32002,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -32174,7 +32186,11 @@
           <t>Accretion expense 12</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -33772,7 +33788,11 @@
           <t>Deferred income tax expense 20</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -33960,7 +33980,11 @@
           <t>Accretion expense 13</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -36458,7 +36482,11 @@
           <t>Deferred income tax expense (recovery) [Note 20]</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -37200,7 +37228,11 @@
           <t>Decrease in long-term debt</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
@@ -38030,7 +38062,11 @@
           <t>Deferred income tax expense (recovery) [Note 18]</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -39318,7 +39354,11 @@
           <t>Deferred income tax expense (recovery) [Note 17]</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -40400,7 +40440,11 @@
           <t>Deferred income tax expense (recovery) [Note 17]</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E346" t="inlineStr">
         <is>
           <t>-</t>
@@ -42390,7 +42434,11 @@
           <t>Deferred income tax expense (recovery) [Note 17]</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
@@ -47400,7 +47448,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>
@@ -48158,7 +48210,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E428" s="5" t="n">
         <v>-0.421</v>
       </c>
@@ -49108,7 +49164,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E438" s="5" t="n">
         <v>0.249979</v>
       </c>
